--- a/jira_export_2026-08-03.xlsx
+++ b/jira_export_2026-08-03.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0 h</t>
+          <t>4 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -4074,32 +4074,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4109,34 +4109,34 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -4146,32 +4146,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
@@ -4197,16 +4197,16 @@
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4218,12 +4218,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4269,16 +4269,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4290,32 +4290,32 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
@@ -4341,16 +4341,16 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4362,27 +4362,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4397,32 +4397,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4434,12 +4434,12 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -4485,16 +4485,16 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4506,32 +4506,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4557,16 +4557,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4578,27 +4578,27 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4629,16 +4629,16 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>416.475</v>
+        <v>700</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4650,32 +4650,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4701,16 +4701,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4722,12 +4722,12 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4773,16 +4773,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
@@ -4794,12 +4794,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4845,16 +4845,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4866,12 +4866,12 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4917,16 +4917,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4938,12 +4938,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -5010,32 +5010,32 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5061,16 +5061,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5082,27 +5082,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5133,16 +5133,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5205,16 +5205,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5226,32 +5226,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5298,32 +5298,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5349,16 +5349,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>1320</v>
+        <v>725</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5370,12 +5370,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5385,11 +5385,13 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
@@ -5408,27 +5410,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5440,22 +5442,22 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E66" s="15" t="n">
@@ -5473,32 +5475,32 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>401</v>
+        <v>1212</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5510,12 +5512,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5548,27 +5550,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5580,22 +5582,22 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E68" s="15" t="n">
@@ -5603,7 +5605,7 @@
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5613,32 +5615,32 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5650,22 +5652,22 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5673,7 +5675,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5683,12 +5685,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5699,49 +5701,191 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N69" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J70" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K70" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-28023</t>
         </is>
       </c>
-      <c r="M69" s="11" t="inlineStr">
+      <c r="M70" s="15" t="inlineStr">
         <is>
           <t>454387</t>
         </is>
       </c>
-      <c r="N69" s="12" t="n">
+      <c r="N70" s="16" t="n">
         <v>557.145</v>
       </c>
-      <c r="O69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="O70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14798</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
+      <c r="N71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr"/>
-      <c r="C70" s="17" t="inlineStr"/>
-      <c r="D70" s="17" t="inlineStr"/>
-      <c r="E70" s="17" t="inlineStr"/>
-      <c r="F70" s="17" t="inlineStr"/>
-      <c r="G70" s="17" t="inlineStr"/>
-      <c r="H70" s="17" t="inlineStr"/>
-      <c r="I70" s="17" t="inlineStr"/>
-      <c r="J70" s="17" t="inlineStr"/>
-      <c r="K70" s="17" t="inlineStr"/>
-      <c r="L70" s="17" t="inlineStr"/>
-      <c r="M70" s="17" t="inlineStr"/>
-      <c r="N70" s="18" t="n">
+      <c r="B72" s="17" t="inlineStr"/>
+      <c r="C72" s="17" t="inlineStr"/>
+      <c r="D72" s="17" t="inlineStr"/>
+      <c r="E72" s="17" t="inlineStr"/>
+      <c r="F72" s="17" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr"/>
+      <c r="H72" s="17" t="inlineStr"/>
+      <c r="I72" s="17" t="inlineStr"/>
+      <c r="J72" s="17" t="inlineStr"/>
+      <c r="K72" s="17" t="inlineStr"/>
+      <c r="L72" s="17" t="inlineStr"/>
+      <c r="M72" s="17" t="inlineStr"/>
+      <c r="N72" s="18" t="n">
         <v>61735.894</v>
       </c>
-      <c r="O70" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="18" t="n"/>
+      <c r="O72" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:P4"/>
@@ -5811,6 +5955,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6385,16 +6531,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0</v>
@@ -6404,7 +6550,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6592,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -6697,12 +6843,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -6718,7 +6864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0 clôture(s) : 0 projet(s), 0 rework</t>
+          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -6755,32 +6901,92 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32902</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMUNE DE BALARUC-LES-BAINS </t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34537</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE BRON] - Remplacement de leur matériel par des PA</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BRON</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n">
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-08-03.xlsx
+++ b/jira_export_2026-08-03.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>4 h</t>
+          <t>14 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2253,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -5582,12 +5582,12 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E68" s="15" t="n">
@@ -5615,34 +5615,34 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="16" t="n">
@@ -5652,22 +5652,22 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E70" s="15" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5771,16 +5771,16 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5792,12 +5792,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5820,70 +5820,140 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N71" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-14798</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="H72" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>05/04/2024</t>
         </is>
       </c>
-      <c r="J71" s="11" t="n">
+      <c r="J72" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="K71" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
+      <c r="K72" s="15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-28003</t>
         </is>
       </c>
-      <c r="M71" s="11" t="inlineStr">
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>412981</t>
         </is>
       </c>
-      <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="N72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr"/>
-      <c r="C72" s="17" t="inlineStr"/>
-      <c r="D72" s="17" t="inlineStr"/>
-      <c r="E72" s="17" t="inlineStr"/>
-      <c r="F72" s="17" t="inlineStr"/>
-      <c r="G72" s="17" t="inlineStr"/>
-      <c r="H72" s="17" t="inlineStr"/>
-      <c r="I72" s="17" t="inlineStr"/>
-      <c r="J72" s="17" t="inlineStr"/>
-      <c r="K72" s="17" t="inlineStr"/>
-      <c r="L72" s="17" t="inlineStr"/>
-      <c r="M72" s="17" t="inlineStr"/>
-      <c r="N72" s="18" t="n">
+      <c r="B73" s="17" t="inlineStr"/>
+      <c r="C73" s="17" t="inlineStr"/>
+      <c r="D73" s="17" t="inlineStr"/>
+      <c r="E73" s="17" t="inlineStr"/>
+      <c r="F73" s="17" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr"/>
+      <c r="H73" s="17" t="inlineStr"/>
+      <c r="I73" s="17" t="inlineStr"/>
+      <c r="J73" s="17" t="inlineStr"/>
+      <c r="K73" s="17" t="inlineStr"/>
+      <c r="L73" s="17" t="inlineStr"/>
+      <c r="M73" s="17" t="inlineStr"/>
+      <c r="N73" s="18" t="n">
         <v>61735.894</v>
       </c>
-      <c r="O72" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="18" t="n">
+      <c r="O73" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5957,6 +6027,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6531,26 +6602,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>2.75</v>
+        <v>6.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6663,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>0.75</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-03.xlsx
+++ b/jira_export_2026-08-03.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>14 h</t>
+          <t>23 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -4121,7 +4121,7 @@
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -4650,27 +4650,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4690,29 +4690,21 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M55" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4722,32 +4714,32 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -4757,12 +4749,12 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
@@ -4773,16 +4765,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
@@ -4794,12 +4786,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4809,12 +4801,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4845,16 +4837,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4866,12 +4858,12 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -4881,12 +4873,12 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4906,7 +4898,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4917,16 +4909,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4938,12 +4930,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4953,12 +4945,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4978,7 +4970,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4989,16 +4981,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -5010,12 +5002,12 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -5025,12 +5017,12 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5050,27 +5042,27 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5082,32 +5074,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5117,12 +5109,12 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5133,16 +5125,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5154,27 +5146,27 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5194,7 +5186,7 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5205,16 +5197,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5277,16 +5269,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5298,32 +5290,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5333,32 +5325,32 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5370,32 +5362,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5405,12 +5397,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5421,16 +5413,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1320</v>
+        <v>725</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5442,12 +5434,12 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -5457,11 +5449,13 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
@@ -5480,29 +5474,29 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
@@ -5512,26 +5506,28 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
@@ -5545,34 +5541,34 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5582,26 +5578,28 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
@@ -5620,23 +5618,23 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>2.75</v>
+        <v>0.1</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
@@ -5652,26 +5650,28 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
@@ -5685,34 +5685,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5722,30 +5722,32 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5755,32 +5757,32 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>240</v>
+        <v>1320</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5792,22 +5794,22 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5825,32 +5827,32 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>557.145</v>
+        <v>1212</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5862,22 +5864,22 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E72" s="15" t="n">
@@ -5890,70 +5892,770 @@
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K72" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-30081</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>00152628</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-22757</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>BREST METROPOLE</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30080</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>00152635</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-22757</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Brest Métropole</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="J74" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K74" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-30079</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>00152632</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-22757</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>BREST METROPOLE</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
+      <c r="N75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-21661</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>[Grand Dax] - Pastell</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>GRAND DAX</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>07/05/2025</t>
+        </is>
+      </c>
+      <c r="J76" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-21222</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>ISSY LES MOULINEAUX</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>23/04/2025</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
+      <c r="N77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-20907</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J78" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N78" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N79" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14798</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H72" s="15" t="inlineStr">
+      <c r="H81" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>05/04/2024</t>
         </is>
       </c>
-      <c r="J72" s="15" t="n">
+      <c r="J81" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="K72" s="15" t="n">
+      <c r="K81" s="11" t="n">
         <v>1.75</v>
       </c>
-      <c r="L72" s="15" t="inlineStr">
+      <c r="L81" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-28003</t>
         </is>
       </c>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="M81" s="11" t="inlineStr">
         <is>
           <t>412981</t>
         </is>
       </c>
-      <c r="N72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="N81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>19/09/2023</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K82" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B73" s="17" t="inlineStr"/>
-      <c r="C73" s="17" t="inlineStr"/>
-      <c r="D73" s="17" t="inlineStr"/>
-      <c r="E73" s="17" t="inlineStr"/>
-      <c r="F73" s="17" t="inlineStr"/>
-      <c r="G73" s="17" t="inlineStr"/>
-      <c r="H73" s="17" t="inlineStr"/>
-      <c r="I73" s="17" t="inlineStr"/>
-      <c r="J73" s="17" t="inlineStr"/>
-      <c r="K73" s="17" t="inlineStr"/>
-      <c r="L73" s="17" t="inlineStr"/>
-      <c r="M73" s="17" t="inlineStr"/>
-      <c r="N73" s="18" t="n">
+      <c r="B83" s="17" t="inlineStr"/>
+      <c r="C83" s="17" t="inlineStr"/>
+      <c r="D83" s="17" t="inlineStr"/>
+      <c r="E83" s="17" t="inlineStr"/>
+      <c r="F83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr"/>
+      <c r="H83" s="17" t="inlineStr"/>
+      <c r="I83" s="17" t="inlineStr"/>
+      <c r="J83" s="17" t="inlineStr"/>
+      <c r="K83" s="17" t="inlineStr"/>
+      <c r="L83" s="17" t="inlineStr"/>
+      <c r="M83" s="17" t="inlineStr"/>
+      <c r="N83" s="18" t="n">
         <v>61735.894</v>
       </c>
-      <c r="O73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="18" t="n">
+      <c r="O83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6028,6 +6730,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6602,26 +7314,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -6663,7 +7375,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>6.75</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
